--- a/figma-visual-testing/templates/figma_visual_tests_template.xlsx
+++ b/figma-visual-testing/templates/figma_visual_tests_template.xlsx
@@ -423,25 +423,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="45" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="45" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,65 +463,70 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Scenario Name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Baseline Env Name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Viewport</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Skip</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>App Name</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Baseline Batch URL</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Error Message</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Locator</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Comparison Batch URL</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Validation Status</t>
         </is>
@@ -555,6 +561,7 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -572,43 +579,44 @@
           <t>https://uat.example.com/cards</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
         <is>
           <t>cards-component</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>cards-component-custom-baseline</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>1280x1024</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>png</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>#main-content &gt; div.cards-section</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -626,12 +634,12 @@
           <t>Home Screen</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
         <is>
           <t>android-home-screen</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -643,11 +651,12 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/abc123XYZ/My-Project?node-id=99-111</t>
+          <t>https://www.figma.com/design/abc123XYZ/My-Project?node-id=20-1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -657,19 +666,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://uat.example.com/not-ready-yet</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>https://uat.example.com/home</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>applitools-web-flow</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Applitools Home</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -677,6 +690,120 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/abc123XYZ/My-Project?node-id=20-2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://uat.example.com/whats-new</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>applitools-web-flow</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Whats New</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/abc123XYZ/My-Project?node-id=20-3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://uat.example.com/integrate</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>applitools-web-flow</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Integrate</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/abc123XYZ/My-Project?node-id=99-111</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://uat.example.com/not-ready-yet</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/figma-visual-testing/templates/figma_visual_tests_template.xlsx
+++ b/figma-visual-testing/templates/figma_visual_tests_template.xlsx
@@ -634,7 +634,11 @@
           <t>Home Screen</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>android-home-screen</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>android-home-screen</t>

--- a/figma-visual-testing/templates/figma_visual_tests_template.xlsx
+++ b/figma-visual-testing/templates/figma_visual_tests_template.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,22 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-        <bgColor rgb="00DDEBF7"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,108 +415,89 @@
   </sheetPr>
   <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="65" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="45" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="45" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Figma URL</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>App URL / Screen Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Scenario Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Baseline Env Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Viewport</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Skip</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Locator</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>App Name</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Baseline Batch URL</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Error Message</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Locator</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Comparison Batch URL</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Validation Status</t>
         </is>
@@ -548,20 +519,6 @@
           <t>https://uat.example.com/homepage</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -579,7 +536,6 @@
           <t>https://uat.example.com/cards</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>cards-component</t>
@@ -605,18 +561,11 @@
           <t>png</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>#main-content &gt; div.cards-section</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -644,18 +593,6 @@
           <t>android-home-screen</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -683,18 +620,6 @@
           <t>Applitools Home</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -722,18 +647,6 @@
           <t>Whats New</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -761,18 +674,6 @@
           <t>Integrate</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -790,24 +691,11 @@
           <t>https://uat.example.com/not-ready-yet</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Skip</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
